--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_30-07-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_30-07-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>£17.39 presale price: £26.0</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -901,17 +901,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£16.70</t>
+          <t>£16.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£16.70</t>
+          <t>£16.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£16.70</t>
+          <t>£16.60</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
